--- a/matome.xlsx
+++ b/matome.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑤_廃棄物管理知識" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑥_過去問テーマ検索表(16年560問)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑦_出題基準値・数値ルール一覧" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⑧_今年の最新動向(R8)" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="B2:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -502,7 +503,6 @@
     <col width="65" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -517,7 +517,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -684,6 +683,28 @@
       <c r="E13" s="6" t="inlineStr">
         <is>
           <t>試験によく出る「数字の引っかけ」「測定原理」「周期ルール」を直前に総チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>⑧_今年の最新動向(R8)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>廃棄物・水質の最新統計（R5〜R7年度）、R8改正廃棄物処理法・PCB特措法・資源有効利用促進法、第五次循環基本計画の目標値、R8年版環境白書、レジオネラ症の動向</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>直近の統計・法改正からの出題に備えて、試験前に数値と施行時期を確認</t>
         </is>
       </c>
     </row>
@@ -698,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="B2:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -710,7 +731,6 @@
     <col width="65" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -725,7 +745,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -1183,7 +1202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="B2:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1195,7 +1214,6 @@
     <col width="54" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1210,7 +1228,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -1604,7 +1621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="B2:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1616,7 +1633,6 @@
     <col width="54" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1631,7 +1647,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -1922,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="B2:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1934,7 +1949,6 @@
     <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1949,7 +1963,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -2240,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J565"/>
+  <dimension ref="B2:J565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2255,7 +2268,6 @@
     <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2270,7 +2282,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -27529,7 +27540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -27542,7 +27553,6 @@
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -27557,7 +27567,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
@@ -28702,6 +28711,705 @@
       <c r="H35" s="5" t="inlineStr">
         <is>
           <t>H24, H25, H26, R1再, R3, R4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>衛生工学一次試験 今年おさえる最新動向（統計・法改正・白書）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>廃棄物・水質の最新統計、R8年の法改正（廃棄物処理法・PCB特措法・資源有効利用促進法）、環境白書、レジオネラ症の動向</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>分野・ブロック</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>項目・テーマ</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>最新の数値・内容</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>時点・根拠</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>試験でのポイント</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>関連する細目</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>一般廃棄物の排出・処理状況</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>・総排出量: 3,811万t（2%減少）
+・1人1日あたり排出量: 839g（前年851g）
+・リサイクル率: 19.3%（0.2ポイント低下）
+・焼却施設数: 991（低下）
+・最終処分量: 306万t
+・総資源化量: 738万t
+・最終処分場の残余年数: 24.9年（微増）</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>R6年度実績（1人1日あたり排出量・最終処分量・総資源化量）</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>総排出量・1人1日あたり排出量・リサイクル率は減少/低下、残余年数は微増</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>排出量・処理状況の統計</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>産業廃棄物の排出・処理状況</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>・総排出量: 3億6,725万t（680万t減少）
+・再生利用: 2億79万t（54.7%）
+・減量化: 1億5,772万t（42.9%）
+・最終処分: 875万t（2.4%）
+・種類別: 汚泥42.1%、動物のふん尿21.9%、がれき類16.5%
+・最終処分場の残余年数: 20.3年</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>R5年度実績（再生利用・減量化・最終処分の内訳）</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>種類別の上位3つ（汚泥 &gt; 動物のふん尿 &gt; がれき類）</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>排出量・処理状況の統計</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>R8改正廃棄物処理法（スクラップヤード規制）</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>・スクラップヤード（金属、プラスチックなどの有価物）に許可制を導入
+・環境汚染のおそれのある物品は国内再生が原則
+・輸出には環境大臣の確認が必要（これまでは承認不要）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>R8改正</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>背景: 鉄スクラップの輸出 年約770万t、再生プラスチックは国内利用量の約3倍が海外に流出（R8年版環境白書）</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>廃棄物処理法・制度・処理施設・その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>R8改正廃棄物処理法（非常災害廃棄物）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>・市町村の一般廃棄物処理計画に、非常災害時の適正処理についての記載が義務
+・都道府県・市町村に、処理業者などとの災害支援協定の締結が努力義務
+・市町村からの災害廃棄物処理の委託を再々委託まで整備
+・非常災害廃棄物の処理施設の設置届出で、生活環境影響調査の書類を省略可能（建築基準法51条の許可は別途必要）
+・非常災害廃棄物の最終処分場: 都道府県知事が申請に基づき設置者を指定。指定されると市町村からの委託を正当な理由なく拒否できない（更新期間5年）
+・JESCOに非常災害廃棄物に関する事業が加わり、専門人材の派遣が可能に</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>R8.9.16施行済み</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>処理計画への記載は「義務」、災害支援協定は「努力義務」の区別</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>災害廃棄物・指定廃棄物</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>PCB特措法改正</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>・JESCOの高濃度PCB処理事業はR8.3末で終了
+・低濃度PCBは旧法の処分期限がR9.3末。R9.4以降は個別の処分期間による新制度
+1) 一律の処分期限を改め、廃棄物ごとに期間を定める（高濃度: 5年以内で定める期間、低濃度: 使用終了日や判明した日から5年以内などの範囲で定める期間）
+2) 低濃度PCBを使用した製品等の所有事業者は、都道府県知事への届出と管理が必要
+3) 高濃度PCBの処分は、民間の能力を有する施設で処理
+4) JESCO法からPCB処理についての条文を削除</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>R9.4.1施行</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>廃棄物処理法・制度・処理施設・その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>改正資源有効利用促進法</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>1) 一定以上の製造業者は、自動車・家電4品目・容器包装で再生プラスチックの利用目標を計画して提出（R9年度〜）、定期報告（R10年度〜）
+2) 環境配慮設計を認定し、製品への表示等が可能に
+3) 指定再資源化製品（モバイルバッテリー・携帯電話・加熱式たばこデバイス）: 高い回収目標を掲げて自主回収・再資源化事業計画の認定を受けたメーカー等は業許可が不要。認定事業者に委託する場合に限りマニフェスト交付も不要
+4) サーキュラーエコノミー（CE）コマース事業者を新設し、資源有効活用に関する基準を設定（家電4品、オフィス家具、複写機が対象）</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>R8.4.1施行</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>第五次循環型社会形成推進基本計画（2030年度目標と最新値）</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>【2030年度目標】
+・資源生産性: 約60万円/t
+・1人あたり天然資源消費量: 約11t/人・年
+・再生可能資源・循環資源の投入割合: 約34%
+・入口側の循環利用率: 約19%
+・出口側の循環利用率: 約44%
+・最終処分量: 約1,100万t/年
+・一般廃棄物最終処分場の残余年数: 2020年度の水準（22年分）を維持
+【2022年度の値（R7年版白書）】入口側の循環利用率 約16.3%／投入割合 約29.1%／最終処分量 約1,250万t
+【2023年度の値（第1回点検、R8.9.17公表）】資源生産性 約50.9万円/t／入口側 約17.0%／出口側 約43.6%（2013年度の46.1%がピーク）／最終処分量 2000年度比 約79%減</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>第五次循環基本計画</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会
+排出量・処理状況の統計</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>食品ロス</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>・食品ロス量: 461万t（前年464万t）
+・事業系: 237万t（同231万t）
+・家庭系: 224万t（同233万t）
+・事業系は2000年度比57%減。2030年度に60%減（219万t）が目標</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>R6年度推計</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会
+排出量・処理状況の統計</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>産業廃棄物の不法投棄等</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>・新規不法投棄: 106件（前年100件）・1.4万t（同4.2万t）
+・不適正処理: 113件（同121件）・6.0万t
+・残存: 2,920件・999.1万t
+・不法投棄の種類は件数で建設系が約74%</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>R6年度</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>排出量・処理状況の統計
+産業廃棄物管理票（マニフェスト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>家電リサイクル法の法定再商品化率</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>・エアコン: 80%
+・ブラウン管テレビ: 55%
+・液晶・プラズマテレビ: 74%
+・冷蔵庫・冷凍庫: 70%
+・洗濯機・衣類乾燥機: 82%</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>家電リサイクル法</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>R8年版環境白書</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>・テーマ: 循環経済（サーキュラーエコノミー）で日本列島を強く豊かに
+・鉄スクラップの輸出 年約770万t／再生プラスチックは国内利用量の約3倍が海外に流出
+・再資源化事業等高度化法: 3年で100件以上の事業認定を目指す</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>R8.6.5公表</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>スクラップヤード規制の背景として押さえる</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>廃棄物管理</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>プラスチック条約（国際動向）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>・INC5.2（2025.8）は合意見送り
+・INC5.3（2026.2）も実質的な交渉なし
+・条約は未成立</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2026年時点</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>リサイクル・循環型社会</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>公共用水域の環境基準達成率</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>・河川BOD: 93.9%（前年93.8%）
+・湖沼COD: 50.8%（同52.5%）
+・海域COD: 78.2%（同78.7%）
+・大腸菌数の適合率: 河川60.0%／湖沼97.4%／海域87.5%</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>R6年度</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>達成率は 河川 &gt; 海域 &gt; 湖沼</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>環境基準・排水基準
+水質指標・試験方法・測定</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>PFOS・PFOA の水道水質基準</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>・水道水質基準に昇格
+・PFOSとPFOAの合算で 0.00005mg/L 以下</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>R8.4.1施行</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>環境基準・排水基準
+水質指標・試験方法・測定</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>汚水処理人口普及率</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>・汚水処理人口普及率: 94.0%（前年93.7%）
+・内訳: 下水道82.2%／農業集落排水施設等2.2%／浄化槽9.5%／コミュニティ・プラント0.1%</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>R7年度末</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>浄化槽
+活性汚泥・生物処理</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>ほう素・ふっ素・硝酸性窒素等の排水基準</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>・暫定排水基準: R7.6.30が期限。7業種は一部基準値を強化してR10.9.30まで延長（旅館業・下水道業は当分の間の適用）
+・一般排水基準: ほう素 10mg/L／ふっ素 8mg/L／硝酸性窒素等 100mg/L（海域以外）</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>R7.6.30〜</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>環境基準・排水基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>水質管理</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>底層溶存酸素量の環境基準</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>・生物1: 4.0mg/L以上
+・生物2: 3.0mg/L以上</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>環境基準</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>環境基準・排水基準
+水質指標・試験方法・測定</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>建築物衛生法の管理基準</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>・新たな改正は確認できず
+・R4.4改正の数値を押さえる: 一酸化炭素 6ppm以下、温度 18℃以上28℃以下</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>R4.4改正</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>建築物衛生法・衛生基準
+室内空気質・健康影響・衛生動物</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>建築環境・設備・建築物衛生管理</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>レジオネラ症の発生動向</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>・2013〜2023年の届出: 20,378例
+・国内感染 88.6%／肺炎型 94.3%／ポンティアック熱型 4.8%／男性 81.9%／届出時死亡 255例
+・診断は尿中抗原検出が95.6%
+・感染源: 入浴施設、冷却塔、加湿器など。生物膜（バイオフィルム）ができると増殖
+・感染症法の4類感染症・全数把握
+・2025年の年間届出数は確認できず</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2013〜2023年</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>R2年度以降ほぼ毎年出題</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>レジオネラ・感染症</t>
         </is>
       </c>
     </row>
